--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.326155280104</v>
+        <v>3.790500233016901</v>
       </c>
       <c r="D2" t="n">
-        <v>24.1649337842461</v>
+        <v>3.926801739939991</v>
       </c>
       <c r="E2" t="n">
-        <v>2.733102408835967</v>
+        <v>0.4441291414358446</v>
       </c>
       <c r="F2" t="n">
-        <v>7.343465409050411</v>
+        <v>1.193313128970692</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.79236009777594</v>
+        <v>4.67875851588859</v>
       </c>
       <c r="D3" t="n">
-        <v>38.85186460234692</v>
+        <v>6.313427997881375</v>
       </c>
       <c r="E3" t="n">
-        <v>2.733102408835967</v>
+        <v>0.4441291414358446</v>
       </c>
       <c r="F3" t="n">
-        <v>7.343465409050411</v>
+        <v>1.193313128970692</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
